--- a/artfynd/A 60275-2024 artfynd.xlsx
+++ b/artfynd/A 60275-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,222 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123283846</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58123</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mo, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>433947</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6598551</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Väse</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Charlotta Eriksson Molin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Charlotta Eriksson Molin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123284117</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väse-Mo, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>434041</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6598473</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Väse</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotta Eriksson Molin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Charlotta Eriksson Molin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60275-2024 artfynd.xlsx
+++ b/artfynd/A 60275-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123283846</v>
+        <v>123284117</v>
       </c>
       <c r="B3" t="n">
-        <v>58123</v>
+        <v>57484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,28 +825,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mo, Vrm</t>
+          <t>Väse-Mo, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433947</v>
+        <v>434041</v>
       </c>
       <c r="R3" t="n">
-        <v>6598551</v>
+        <v>6598473</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123284117</v>
+        <v>123283846</v>
       </c>
       <c r="B4" t="n">
-        <v>57484</v>
+        <v>58123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,20 +910,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,24 +931,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väse-Mo, Vrm</t>
+          <t>Mo, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434041</v>
+        <v>433947</v>
       </c>
       <c r="R4" t="n">
-        <v>6598473</v>
+        <v>6598551</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 60275-2024 artfynd.xlsx
+++ b/artfynd/A 60275-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123284117</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>123283846</v>
       </c>
       <c r="B4" t="n">
-        <v>58123</v>
+        <v>58126</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60275-2024 artfynd.xlsx
+++ b/artfynd/A 60275-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284117</v>
+        <v>123283846</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>58126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,24 +825,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väse-Mo, Vrm</t>
+          <t>Mo, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434041</v>
+        <v>433947</v>
       </c>
       <c r="R3" t="n">
-        <v>6598473</v>
+        <v>6598551</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123283846</v>
+        <v>123284117</v>
       </c>
       <c r="B4" t="n">
-        <v>58126</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,20 +914,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -931,28 +935,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mo, Vrm</t>
+          <t>Väse-Mo, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433947</v>
+        <v>434041</v>
       </c>
       <c r="R4" t="n">
-        <v>6598551</v>
+        <v>6598473</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 60275-2024 artfynd.xlsx
+++ b/artfynd/A 60275-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123283846</v>
+        <v>123284117</v>
       </c>
       <c r="B3" t="n">
-        <v>58126</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,28 +825,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mo, Vrm</t>
+          <t>Väse-Mo, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433947</v>
+        <v>434041</v>
       </c>
       <c r="R3" t="n">
-        <v>6598551</v>
+        <v>6598473</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123284117</v>
+        <v>123283846</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>58126</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,20 +910,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,24 +931,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väse-Mo, Vrm</t>
+          <t>Mo, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434041</v>
+        <v>433947</v>
       </c>
       <c r="R4" t="n">
-        <v>6598473</v>
+        <v>6598551</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 60275-2024 artfynd.xlsx
+++ b/artfynd/A 60275-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123284117</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>123283846</v>
       </c>
       <c r="B4" t="n">
-        <v>58126</v>
+        <v>58132</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60275-2024 artfynd.xlsx
+++ b/artfynd/A 60275-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284117</v>
+        <v>123283846</v>
       </c>
       <c r="B3" t="n">
-        <v>57493</v>
+        <v>58135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,24 +825,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väse-Mo, Vrm</t>
+          <t>Mo, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434041</v>
+        <v>433947</v>
       </c>
       <c r="R3" t="n">
-        <v>6598473</v>
+        <v>6598551</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123283846</v>
+        <v>123284117</v>
       </c>
       <c r="B4" t="n">
-        <v>58132</v>
+        <v>57496</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,20 +914,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -931,28 +935,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mo, Vrm</t>
+          <t>Väse-Mo, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433947</v>
+        <v>434041</v>
       </c>
       <c r="R4" t="n">
-        <v>6598551</v>
+        <v>6598473</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 60275-2024 artfynd.xlsx
+++ b/artfynd/A 60275-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123283846</v>
       </c>
       <c r="B3" t="n">
-        <v>58135</v>
+        <v>58136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>123284117</v>
       </c>
       <c r="B4" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
